--- a/SGC-CKN/Excel/02b8cbd6-5408-4b93-8276-650dee406d39_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-114_D800_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/02b8cbd6-5408-4b93-8276-650dee406d39_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-114_D800_14-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-114</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">14h30
@@ -106,10 +106,13 @@
 13/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15h00
@@ -123,7 +126,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">16h00
@@ -151,9 +154,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">19h40
 13/03/2026</t>
   </si>
@@ -165,7 +165,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">21h10
@@ -179,7 +179,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23h50
@@ -196,7 +196,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">00h25
@@ -1205,24 +1205,24 @@
         <v>3.31</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-1.6</v>
@@ -1240,24 +1240,24 @@
         <v>11.13</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="13">
         <v>-11.8</v>
@@ -1275,24 +1275,24 @@
         <v>5.29</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="16">
         <v>-17</v>
@@ -1310,18 +1310,18 @@
         <v>4.06</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>44</v>
@@ -1345,7 +1345,7 @@
         <v>4.58</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1380,7 +1380,7 @@
         <v>0.94</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1654,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1683,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1712,7 +1712,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1825,10 +1825,10 @@
         <v>69</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="34">
         <v>8</v>
